--- a/DocumentacionAuxiliar/Ramas actividad económica.xlsx
+++ b/DocumentacionAuxiliar/Ramas actividad económica.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeimy.castillo\OneDrive - Pontificia Universidad Javeriana\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Documents\Trabajo-Profesional\Javeriana\DocumentacionAuxiliar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787666CA-8A3B-46CA-8E3E-712B68BB1762}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5F6F2F-62D4-4CA5-94BD-48BB8B88D9AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2352" yWindow="0" windowWidth="21864" windowHeight="9072" activeTab="1" xr2:uid="{DB00A854-B32D-4133-B35C-320E9F1175A0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB00A854-B32D-4133-B35C-320E9F1175A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -596,12 +596,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -632,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -650,6 +656,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -669,9 +682,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -709,7 +722,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -815,7 +828,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -957,7 +970,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -996,11 +1009,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1021,7 +1034,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1044,19 +1057,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:2" s="9" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" s="9" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>21</v>
       </c>
     </row>
